--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="166">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Base</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-entry</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -250,50 +250,218 @@
     <t>Base</t>
   </si>
   <si>
-    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.identifiant</t>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.header</t>
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base
+</t>
+  </si>
+  <si>
+    <t>Métadonnées de base</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.header.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
+</t>
+  </si>
+  <si>
+    <t>Patient / Usager</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.subject</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.header.identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t xml:space="preserve">	Identifiant du résultat</t>
-  </si>
-  <si>
-    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.codeIdentification</t>
+    <t>Identifiant de l’entrée</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.identifier</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.header.author[x]</t>
+  </si>
+  <si>
+    <t>author[x] peut correspondre soit à un professionnel, soit à une organisation, soit à un système.</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
+  </si>
+  <si>
+    <t>Exécutant (performer)</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.header.participant[x]</t>
+  </si>
+  <si>
+    <t>Participant</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.header.informant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
+</t>
+  </si>
+  <si>
+    <t>Informateur</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.informant</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.header.date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date/Heure de création par l'auteur</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.date</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
+    <t>Niveau de complétude</t>
+  </si>
+  <si>
+    <t>Statut</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.header.source</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.source</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.header.language</t>
+  </si>
+  <si>
+    <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
+La partie en minuscules indique le code de la langue utilisée (ISO-639-1)
+La partie en majuscules indique le code pays (ISO-3166)</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.language</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.codeIdentification</t>
+  </si>
+  <si>
     <t>Code d'identification de l'analyse ou de l'observation</t>
   </si>
   <si>
-    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.statut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Niveau de complétude</t>
-  </si>
-  <si>
-    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.dateResultat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date et heure de ce résultat</t>
-  </si>
-  <si>
-    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.valeurResultat</t>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.valeurResultat[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+stringQuantityRatioRange</t>
   </si>
   <si>
     <t>Valeur du résultat</t>
@@ -331,63 +499,27 @@
     <t>Laboratoire sous-traitant. Apparaît à ce niveau si et et seulement si ce résultat a été produit par un laboratoire exécutant distinct du laboratoire exécutant déclaré aux niveaux supérieurs.</t>
   </si>
   <si>
-    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.auteur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-auteur
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.commentaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Auteur</t>
-  </si>
-  <si>
-    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.valideur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
+    <t>Commentaire d'interprétation des résultats</t>
+  </si>
+  <si>
+    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.prelevement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-specimen
 </t>
   </si>
   <si>
-    <t>Valideur de ces résultats</t>
-  </si>
-  <si>
-    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.responsable</t>
-  </si>
-  <si>
-    <t>Responsable de cet examen</t>
-  </si>
-  <si>
-    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.dispositifAutomatique</t>
-  </si>
-  <si>
-    <t>Dispositif automatique impliqué dans la production des résultats</t>
-  </si>
-  <si>
-    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.commentaire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-commentaire-er
-</t>
-  </si>
-  <si>
-    <t>Commentaire d'interprétation des résultats</t>
-  </si>
-  <si>
-    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.prelevement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-prelevement
-</t>
-  </si>
-  <si>
     <t>Prélèvement</t>
   </si>
   <si>
     <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.resultatsAnterieurs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base
-</t>
   </si>
   <si>
     <t>Résultats antérieurs. Plusieurs résultats antérieurs peuvent être ajoutés. 
@@ -699,11 +831,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ19"/>
+  <dimension ref="A1:AJ29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="65.046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="65.046875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="83.64453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="83.64453125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -733,7 +865,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="65.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="64.3515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -962,7 +1094,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>79</v>
@@ -1034,10 +1166,10 @@
         <v>73</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>79</v>
@@ -1051,10 +1183,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1062,7 +1194,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>79</v>
@@ -1077,13 +1209,13 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1134,10 +1266,10 @@
         <v>73</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
         <v>79</v>
@@ -1151,10 +1283,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1162,10 +1294,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>73</v>
@@ -1177,13 +1309,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1234,13 +1366,13 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>73</v>
@@ -1251,10 +1383,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1265,7 +1397,7 @@
         <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -1277,13 +1409,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1334,13 +1466,13 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>73</v>
@@ -1351,10 +1483,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1365,7 +1497,7 @@
         <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>73</v>
@@ -1377,13 +1509,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1434,13 +1566,13 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>73</v>
@@ -1451,10 +1583,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1465,7 +1597,7 @@
         <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -1477,13 +1609,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1534,13 +1666,13 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>73</v>
@@ -1551,10 +1683,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1565,7 +1697,7 @@
         <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -1577,13 +1709,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1634,13 +1766,13 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>73</v>
@@ -1651,10 +1783,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1665,7 +1797,7 @@
         <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>73</v>
@@ -1677,13 +1809,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1734,13 +1866,13 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>73</v>
@@ -1751,10 +1883,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1777,13 +1909,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1834,7 +1966,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1851,10 +1983,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1877,13 +2009,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1934,7 +2066,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -1951,10 +2083,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1965,7 +2097,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -1977,13 +2109,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2034,13 +2166,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2051,10 +2183,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2065,7 +2197,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2077,13 +2209,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2134,13 +2266,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2151,10 +2283,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2177,13 +2309,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2234,7 +2366,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2251,10 +2383,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2265,7 +2397,7 @@
         <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>73</v>
@@ -2277,13 +2409,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2334,13 +2466,13 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>73</v>
@@ -2351,10 +2483,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2365,7 +2497,7 @@
         <v>74</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>73</v>
@@ -2377,13 +2509,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2434,13 +2566,13 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>73</v>
@@ -2451,10 +2583,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2465,7 +2597,7 @@
         <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>73</v>
@@ -2477,13 +2609,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2534,13 +2666,13 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>73</v>
@@ -2551,10 +2683,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2577,13 +2709,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2634,7 +2766,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2646,6 +2778,1006 @@
         <v>73</v>
       </c>
       <c r="AJ19" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
